--- a/VT_REG1_ELC_V12.xlsx
+++ b/VT_REG1_ELC_V12.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
-  <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F285464-C26D-4EE5-8AAA-6C1B248B09E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" tabRatio="901" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="EB1" sheetId="133" r:id="rId1"/>
-    <sheet name="RES_ELC" sheetId="152" r:id="rId2"/>
-    <sheet name="Sector_Fuels_ELC" sheetId="140" r:id="rId3"/>
-    <sheet name="Con_ELC" sheetId="143" r:id="rId4"/>
-    <sheet name="Emi" sheetId="149" r:id="rId5"/>
+    <sheet name="EB1" sheetId="133" r:id="rId3"/>
+    <sheet name="RES_ELC" sheetId="152" r:id="rId4"/>
+    <sheet name="Sector_Fuels_ELC" sheetId="140" r:id="rId5"/>
+    <sheet name="Con_ELC" sheetId="143" r:id="rId6"/>
+    <sheet name="Emi" sheetId="149" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
-    <externalReference r:id="rId7"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
@@ -38,20 +38,19 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0" shapeId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -63,7 +62,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -72,7 +70,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -83,7 +80,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -92,7 +88,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -103,7 +98,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -112,7 +106,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -123,7 +116,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -132,7 +124,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -143,7 +134,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -152,7 +142,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -160,13 +149,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="1" shapeId="0">
+    <comment ref="O3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -175,7 +163,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -186,12 +173,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="2" shapeId="0">
+    <comment ref="P3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -201,7 +187,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -211,7 +196,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -221,7 +205,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -231,7 +214,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -241,7 +223,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -251,7 +232,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -259,12 +239,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="2" shapeId="0">
+    <comment ref="Q3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -274,7 +253,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -284,7 +262,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -294,7 +271,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -304,7 +280,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -312,12 +287,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="2" shapeId="0">
+    <comment ref="R3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -328,7 +302,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -337,7 +310,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -345,12 +317,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="P15" authorId="2" shapeId="0">
+    <comment ref="P15" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -361,7 +332,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -370,7 +340,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -381,7 +350,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -390,7 +358,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -401,7 +368,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -410,7 +376,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -421,7 +386,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -430,7 +394,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -438,13 +401,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="1" shapeId="0">
+    <comment ref="Q15" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -453,7 +415,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -463,12 +424,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="R15" authorId="2" shapeId="0">
+    <comment ref="R15" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -478,7 +438,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -488,7 +447,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -498,7 +456,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -507,7 +464,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -517,7 +473,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -526,12 +481,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="2" shapeId="0">
+    <comment ref="J16" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -540,7 +494,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -551,7 +504,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -561,7 +513,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -571,7 +522,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -581,7 +531,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -591,7 +540,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -601,7 +549,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -611,7 +558,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -621,7 +567,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -631,7 +576,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -641,7 +585,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -651,7 +594,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -661,7 +603,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -671,7 +612,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -681,7 +621,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -692,7 +631,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -701,7 +639,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -711,7 +648,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -721,7 +657,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -731,7 +666,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -741,7 +675,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -751,7 +684,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -761,7 +693,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -773,20 +704,19 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -798,7 +728,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -807,7 +736,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -818,7 +746,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -827,7 +754,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -838,7 +764,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -847,7 +772,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -858,7 +782,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -867,7 +790,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -878,7 +800,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -887,7 +808,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -895,13 +815,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="1" shapeId="0">
+    <comment ref="Y3" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -910,7 +829,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -921,12 +839,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z3" authorId="2" shapeId="0">
+    <comment ref="Z3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -936,7 +853,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -946,7 +862,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -956,7 +871,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -966,7 +880,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -976,7 +889,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -986,7 +898,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -994,12 +905,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA3" authorId="2" shapeId="0">
+    <comment ref="AA3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1009,7 +919,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1019,7 +928,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1029,7 +937,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1039,7 +946,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1047,12 +953,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB3" authorId="2" shapeId="0">
+    <comment ref="AB3" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1063,7 +968,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1072,7 +976,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1080,12 +983,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z9" authorId="2" shapeId="0">
+    <comment ref="Z9" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1096,7 +998,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1105,7 +1006,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1116,7 +1016,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1125,7 +1024,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1136,7 +1034,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1145,7 +1042,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1156,7 +1052,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1165,7 +1060,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1173,13 +1067,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA9" authorId="1" shapeId="0">
+    <comment ref="AA9" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1188,7 +1081,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1198,12 +1090,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB9" authorId="2" shapeId="0">
+    <comment ref="AB9" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1213,7 +1104,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1223,7 +1113,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1233,7 +1122,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1242,7 +1130,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1252,7 +1139,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1261,12 +1147,11 @@
         </r>
       </text>
     </comment>
-    <comment ref="T10" authorId="2" shapeId="0">
+    <comment ref="T10" authorId="2">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1275,7 +1160,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1286,7 +1170,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1296,7 +1179,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1306,7 +1188,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1316,7 +1197,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1326,7 +1206,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1336,7 +1215,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1346,7 +1224,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1356,7 +1233,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1366,7 +1242,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1376,7 +1251,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1386,7 +1260,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1396,7 +1269,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1406,7 +1278,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1416,7 +1287,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1427,7 +1297,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1436,7 +1305,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1446,7 +1314,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1456,7 +1323,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1466,7 +1332,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1476,7 +1341,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1486,7 +1350,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1496,7 +1359,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1637,382 +1499,382 @@
     <t>TimeSlice level of Process Activity</t>
   </si>
   <si>
+    <t>VOC</t>
+  </si>
+  <si>
+    <t>Nox</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>Electricity Plants</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Derived Heat</t>
+  </si>
+  <si>
+    <t>ELC</t>
+  </si>
+  <si>
+    <t>Biomass</t>
+  </si>
+  <si>
+    <t>Nuclear Energy</t>
+  </si>
+  <si>
+    <t>Solid Fuels</t>
+  </si>
+  <si>
+    <t>HET</t>
+  </si>
+  <si>
+    <t>SLU</t>
+  </si>
+  <si>
+    <t>WIN</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>BIO</t>
+  </si>
+  <si>
+    <t>NUC</t>
+  </si>
+  <si>
+    <t>OPP</t>
+  </si>
+  <si>
+    <t>HFO</t>
+  </si>
+  <si>
+    <t>NAP</t>
+  </si>
+  <si>
+    <t>GSL</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>KER</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>Sector Name</t>
+  </si>
+  <si>
+    <t>PRE</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Wind energy</t>
+  </si>
+  <si>
+    <t>Total Production</t>
+  </si>
+  <si>
+    <t>LIFE</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>EFF</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>*Units</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>NOX</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Carbon dioxide</t>
+  </si>
+  <si>
+    <t>Thermal</t>
+  </si>
+  <si>
+    <t>Renewable</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>VAROM</t>
+  </si>
+  <si>
+    <t>Emission by sector</t>
+  </si>
+  <si>
+    <t>Hydro power</t>
+  </si>
+  <si>
+    <t>INVCOST</t>
+  </si>
+  <si>
+    <t>OIL</t>
+  </si>
+  <si>
+    <t>GAS</t>
+  </si>
+  <si>
+    <t>Default Units</t>
+  </si>
+  <si>
+    <t>Emissions</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Share-I~UP</t>
+  </si>
+  <si>
+    <t>Commodity</t>
+  </si>
+  <si>
+    <t>Input Share</t>
+  </si>
+  <si>
+    <t>SEASON</t>
+  </si>
+  <si>
     <t>COA</t>
   </si>
   <si>
-    <t>GAS</t>
-  </si>
-  <si>
-    <t>OIL</t>
-  </si>
-  <si>
-    <t>NUC</t>
-  </si>
-  <si>
-    <t>SLU</t>
-  </si>
-  <si>
-    <t>HET</t>
-  </si>
-  <si>
-    <t>ELC</t>
-  </si>
-  <si>
-    <t>Solid Fuels</t>
+    <t>ELE</t>
+  </si>
+  <si>
+    <t>% contribution to PEAK</t>
+  </si>
+  <si>
+    <t>Capacity to Activity Factor</t>
+  </si>
+  <si>
+    <t>Capacity unit</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Currency Unit</t>
+  </si>
+  <si>
+    <t>Power Plant Type</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>Variable O&amp;M Cost</t>
+  </si>
+  <si>
+    <t>Invesctment Cost</t>
+  </si>
+  <si>
+    <t>Utilisation Factor</t>
+  </si>
+  <si>
+    <t>CAP2ACT</t>
+  </si>
+  <si>
+    <t>Peak</t>
+  </si>
+  <si>
+    <t>CALIBRATION</t>
+  </si>
+  <si>
+    <t>Past Investment Capacity</t>
+  </si>
+  <si>
+    <t>Fixed O&amp;M Cost</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>FIXOM</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Power Plants</t>
+  </si>
+  <si>
+    <t>Nuclear</t>
+  </si>
+  <si>
+    <t>REG1</t>
+  </si>
+  <si>
+    <t>Retirement Capacity</t>
+  </si>
+  <si>
+    <t>STOCK</t>
+  </si>
+  <si>
+    <t>Other Petroleum Products</t>
+  </si>
+  <si>
+    <t>Data used in the template to buld the model</t>
+  </si>
+  <si>
+    <t>Total Conversion</t>
+  </si>
+  <si>
+    <t>Motor spirit</t>
+  </si>
+  <si>
+    <t>Petroleum Refineries</t>
+  </si>
+  <si>
+    <t>REF</t>
+  </si>
+  <si>
+    <t>Heat Plants</t>
+  </si>
+  <si>
+    <t>HPL</t>
+  </si>
+  <si>
+    <t>Crude oil</t>
   </si>
   <si>
     <t>Natural Gas</t>
   </si>
   <si>
-    <t>Nuclear Energy</t>
+    <t>Naphtha</t>
+  </si>
+  <si>
+    <t>Kerosenes</t>
+  </si>
+  <si>
+    <t>Diesel oil</t>
+  </si>
+  <si>
+    <t>Heavy Fuel Oil</t>
+  </si>
+  <si>
+    <t>~COMEMI</t>
+  </si>
+  <si>
+    <t>Deafult unit</t>
+  </si>
+  <si>
+    <t>Sector Fuel</t>
+  </si>
+  <si>
+    <t>Solar energy</t>
+  </si>
+  <si>
+    <t>DSL</t>
+  </si>
+  <si>
+    <t>Dynamic coefficients for combustion emissions in power sector</t>
+  </si>
+  <si>
+    <t>User inputs</t>
+  </si>
+  <si>
+    <t>Linked to the Energy Balance</t>
+  </si>
+  <si>
+    <t>Conversion (Power Sector)</t>
+  </si>
+  <si>
+    <t>Reference Energy System (from VEDA-FE Go-To RES feature)</t>
+  </si>
+  <si>
+    <t>PASTI~1980</t>
+  </si>
+  <si>
+    <t>ELC template</t>
+  </si>
+  <si>
+    <t>kt/PJ</t>
   </si>
   <si>
     <t>Industrial Wastes</t>
   </si>
   <si>
-    <t>Derived Heat</t>
+    <t>ESC</t>
+  </si>
+  <si>
+    <t>PJ</t>
+  </si>
+  <si>
+    <t>M€2005</t>
+  </si>
+  <si>
+    <t>TOT</t>
+  </si>
+  <si>
+    <t>Energy Sector Consumption</t>
+  </si>
+  <si>
+    <t>CONVERSION</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>CONVERSION</t>
-  </si>
-  <si>
-    <t>ESC</t>
-  </si>
-  <si>
-    <t>Energy Sector Consumption</t>
-  </si>
-  <si>
-    <t>Electricity Plants</t>
-  </si>
-  <si>
-    <t>HPL</t>
-  </si>
-  <si>
-    <t>Heat Plants</t>
-  </si>
-  <si>
-    <t>REF</t>
-  </si>
-  <si>
-    <t>Petroleum Refineries</t>
-  </si>
-  <si>
-    <t>Total Conversion</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>Sector Name</t>
-  </si>
-  <si>
-    <t>Commodity</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>PJ</t>
-  </si>
-  <si>
-    <t>Currency Unit</t>
-  </si>
-  <si>
-    <t>LIFE</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>FIXOM</t>
-  </si>
-  <si>
-    <t>EFF</t>
-  </si>
-  <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>Efficiency</t>
-  </si>
-  <si>
-    <t>*Units</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Default Units</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Fixed O&amp;M Cost</t>
-  </si>
-  <si>
-    <t>Utilisation Factor</t>
-  </si>
-  <si>
-    <t>Existing</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Emissions</t>
-  </si>
-  <si>
     <t>kt</t>
   </si>
   <si>
+    <t>Lifetime</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
     <t>ENV</t>
   </si>
   <si>
-    <t>CO2</t>
-  </si>
-  <si>
-    <t>Nox</t>
-  </si>
-  <si>
-    <t>VOC</t>
-  </si>
-  <si>
-    <t>Carbon dioxide</t>
-  </si>
-  <si>
-    <t>NOX</t>
-  </si>
-  <si>
-    <t>Sector Fuel</t>
-  </si>
-  <si>
-    <t>PRE</t>
-  </si>
-  <si>
-    <t>Deafult unit</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Emission by sector</t>
-  </si>
-  <si>
-    <t>Capacity unit</t>
-  </si>
-  <si>
-    <t>Power Plants</t>
-  </si>
-  <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>ELE</t>
-  </si>
-  <si>
-    <t>VAROM</t>
-  </si>
-  <si>
-    <t>Total Production</t>
-  </si>
-  <si>
-    <t>Variable O&amp;M Cost</t>
-  </si>
-  <si>
-    <t>Capacity to Activity Factor</t>
-  </si>
-  <si>
-    <t>Power Plant Type</t>
-  </si>
-  <si>
     <t>CHP</t>
   </si>
   <si>
-    <t>Renewable</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>T</t>
+    <t>AFA</t>
+  </si>
+  <si>
+    <t>STOCK~2030</t>
   </si>
   <si>
     <t>Code</t>
   </si>
   <si>
-    <t>Thermal</t>
-  </si>
-  <si>
-    <t>CALIBRATION</t>
-  </si>
-  <si>
-    <t>DAYNITE</t>
-  </si>
-  <si>
-    <t>SEASON</t>
-  </si>
-  <si>
-    <t>Peak</t>
-  </si>
-  <si>
-    <t>% contribution to PEAK</t>
-  </si>
-  <si>
-    <t>Retirement Capacity</t>
-  </si>
-  <si>
-    <t>REG1</t>
-  </si>
-  <si>
-    <t>Nuclear</t>
-  </si>
-  <si>
-    <t>STOCK</t>
-  </si>
-  <si>
-    <t>Crude oil</t>
-  </si>
-  <si>
-    <t>DSL</t>
-  </si>
-  <si>
-    <t>KER</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>GSL</t>
-  </si>
-  <si>
-    <t>NAP</t>
-  </si>
-  <si>
-    <t>HFO</t>
-  </si>
-  <si>
-    <t>OPP</t>
-  </si>
-  <si>
-    <t>Heavy Fuel Oil</t>
-  </si>
-  <si>
-    <t>Other Petroleum Products</t>
-  </si>
-  <si>
-    <t>Kerosenes</t>
-  </si>
-  <si>
-    <t>Motor spirit</t>
-  </si>
-  <si>
-    <t>Naphtha</t>
-  </si>
-  <si>
-    <t>Diesel oil</t>
-  </si>
-  <si>
-    <t>~COMEMI</t>
-  </si>
-  <si>
-    <t>Input Share</t>
-  </si>
-  <si>
-    <t>Share-I~UP</t>
-  </si>
-  <si>
-    <t>M€2005</t>
-  </si>
-  <si>
-    <t>Data used in the template to buld the model</t>
-  </si>
-  <si>
-    <t>kt/PJ</t>
-  </si>
-  <si>
-    <t>User inputs</t>
-  </si>
-  <si>
-    <t>Linked to the Energy Balance</t>
-  </si>
-  <si>
-    <t>Reference Energy System (from VEDA-FE Go-To RES feature)</t>
-  </si>
-  <si>
-    <t>Conversion (Power Sector)</t>
-  </si>
-  <si>
-    <t>STOCK~2030</t>
-  </si>
-  <si>
-    <t>ELC template</t>
-  </si>
-  <si>
-    <t>Dynamic coefficients for combustion emissions in power sector</t>
-  </si>
-  <si>
-    <t>TOT</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>Hydro power</t>
-  </si>
-  <si>
-    <t>Wind energy</t>
-  </si>
-  <si>
-    <t>Solar energy</t>
-  </si>
-  <si>
-    <t>BIO</t>
-  </si>
-  <si>
-    <t>WIN</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>Biomass</t>
-  </si>
-  <si>
-    <t>Lifetime</t>
-  </si>
-  <si>
-    <t>CAP2ACT</t>
-  </si>
-  <si>
-    <t>INVCOST</t>
-  </si>
-  <si>
-    <t>Invesctment Cost</t>
-  </si>
-  <si>
     <t>PASTI~1960</t>
-  </si>
-  <si>
-    <t>PASTI~1980</t>
-  </si>
-  <si>
-    <t>Past Investment Capacity</t>
-  </si>
-  <si>
-    <t>AFA</t>
   </si>
 </sst>
 </file>
@@ -2027,14 +1889,17 @@
     <numFmt numFmtId="190" formatCode="0.0000"/>
     <numFmt numFmtId="195" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2048,11 +1913,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color indexed="12"/>
@@ -2061,40 +1921,12 @@
     </font>
     <font>
       <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
@@ -2116,19 +1948,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2209,12 +2032,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
@@ -2224,7 +2041,7 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="9" tint="-0.249977111117893"/>
+      <color theme="9" tint="-0.249960005283356"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2242,6 +2059,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="9" tint="-0.249950006604195"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -2252,7 +2076,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990010261536"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2264,80 +2142,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599990010261536"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2346,173 +2175,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -2530,7 +2192,64 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -2540,27 +2259,25 @@
         <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2568,260 +2285,456 @@
         <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
     </border>
   </borders>
-  <cellStyleXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+  <cellStyleXfs count="48">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="30" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="30" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="30" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="22"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="25" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="25" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="27" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="25" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="22" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="9" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyFill="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyFill="1" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="28" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="25" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="12" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="11" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="29" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="21" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="3" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="22" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="25" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="22" fillId="9" borderId="0" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="22" fillId="9" borderId="5" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="187" fontId="20" fillId="7" borderId="6" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="7" borderId="0" xfId="26" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="7" borderId="6" xfId="26" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="187" fontId="13" fillId="5" borderId="7" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="7" borderId="17" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="8" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="7" borderId="18" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="9" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="7" borderId="19" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="5" borderId="10" xfId="23" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="14" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="22" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="188" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="4" fillId="16" borderId="0" xfId="16" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="16" borderId="0" xfId="15" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="27" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="9" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="28" applyFill="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="28" applyNumberFormat="1" applyFill="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="30" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="187" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="14" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="15" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="8" fillId="15" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="188" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="9" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="0" xfId="9" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="28" applyFill="1" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="14" borderId="0" xfId="28" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="26" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="28" applyNumberFormat="1">
+      <alignment/>
+      <protection/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="25" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="21" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="3" xfId="21" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="3" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="195" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="195" fontId="25" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="18" fillId="2" borderId="3" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2829,57 +2742,147 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="195" fontId="25" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="18" fillId="2" borderId="3" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
+    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="28" applyNumberFormat="1">
+      <alignment/>
+      <protection/>
+    </xf>
     <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="30">
-    <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
-    <cellStyle name="40% - Accent3" xfId="2" builtinId="39"/>
-    <cellStyle name="Accent2" xfId="3" builtinId="33"/>
-    <cellStyle name="Calculation" xfId="4" builtinId="22"/>
-    <cellStyle name="Comma 2" xfId="5"/>
-    <cellStyle name="Good" xfId="6" builtinId="26"/>
-    <cellStyle name="Input" xfId="7" builtinId="20"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28"/>
+  <cellStyles count="34">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="9"/>
-    <cellStyle name="Normal 2" xfId="10"/>
-    <cellStyle name="Normal 4" xfId="11"/>
-    <cellStyle name="Normal 4 2" xfId="12"/>
-    <cellStyle name="Normal 8" xfId="13"/>
-    <cellStyle name="Normal 9 2" xfId="14"/>
-    <cellStyle name="Normale_B2020" xfId="15"/>
-    <cellStyle name="Percent" xfId="16" builtinId="5"/>
-    <cellStyle name="Percent 2" xfId="17"/>
-    <cellStyle name="Percent 3" xfId="18"/>
-    <cellStyle name="Percent 3 2" xfId="19"/>
-    <cellStyle name="Percent 3 3" xfId="20"/>
-    <cellStyle name="Percent 3 4" xfId="21"/>
-    <cellStyle name="Percent 4" xfId="22"/>
-    <cellStyle name="Percent 4 2" xfId="23"/>
-    <cellStyle name="Percent 4 3" xfId="24"/>
-    <cellStyle name="Percent 4 4" xfId="25"/>
-    <cellStyle name="Percent 5" xfId="26"/>
-    <cellStyle name="Percent 6" xfId="27"/>
-    <cellStyle name="Percent 7" xfId="28"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="29"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="20% - Accent5" xfId="20" builtinId="46"/>
+    <cellStyle name="40% - Accent3" xfId="21" builtinId="39"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33"/>
+    <cellStyle name="Calculation" xfId="23" builtinId="22"/>
+    <cellStyle name="Comma 2" xfId="24"/>
+    <cellStyle name="Good" xfId="25" builtinId="26"/>
+    <cellStyle name="Input" xfId="26" builtinId="20"/>
+    <cellStyle name="Neutral" xfId="27" builtinId="28"/>
+    <cellStyle name="Normal 10" xfId="28"/>
+    <cellStyle name="Normal 2" xfId="29"/>
+    <cellStyle name="Normal 4" xfId="30"/>
+    <cellStyle name="Normal 4 2" xfId="31"/>
+    <cellStyle name="Normal 8" xfId="32"/>
+    <cellStyle name="Normal 9 2" xfId="33"/>
+    <cellStyle name="Normale_B2020" xfId="34"/>
+    <cellStyle name="Percent 2" xfId="35"/>
+    <cellStyle name="Percent 3" xfId="36"/>
+    <cellStyle name="Percent 3 2" xfId="37"/>
+    <cellStyle name="Percent 3 3" xfId="38"/>
+    <cellStyle name="Percent 3 4" xfId="39"/>
+    <cellStyle name="Percent 4" xfId="40"/>
+    <cellStyle name="Percent 4 2" xfId="41"/>
+    <cellStyle name="Percent 4 3" xfId="42"/>
+    <cellStyle name="Percent 4 4" xfId="43"/>
+    <cellStyle name="Percent 5" xfId="44"/>
+    <cellStyle name="Percent 6" xfId="45"/>
+    <cellStyle name="Percent 7" xfId="46"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="47"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2892,7 +2895,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -2911,7 +2914,7 @@
         <xdr:cNvPr id="56975" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07B54768-2264-459D-AAAF-4E7CAD4688C6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07b54768-2264-459d-aaaf-4e7cad4688c6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2920,14 +2923,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2937,9 +2933,7 @@
           <a:off x="123825" y="962025"/>
           <a:ext cx="800100" cy="2238375"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -2985,7 +2979,7 @@
         <xdr:cNvPr id="56976" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{092998F4-DAF5-4AB5-A34B-DFA9CC7FF7F7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{092998f4-daf5-4ab5-a34b-dfa9cc7ff7f7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2994,14 +2988,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3011,9 +2998,7 @@
           <a:off x="1552575" y="18926175"/>
           <a:ext cx="4019550" cy="1905000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3059,7 +3044,7 @@
         <xdr:cNvPr id="56977" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD288841-D70D-4C2E-9A6A-06C46B032C2B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ad288841-d70d-4c2e-9a6a-06c46b032c2b}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3068,14 +3053,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3085,9 +3063,7 @@
           <a:off x="1552575" y="1104900"/>
           <a:ext cx="6524625" cy="3905250"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3133,7 +3109,7 @@
         <xdr:cNvPr id="56978" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7EDBE9C-2FFC-4928-AE9B-DF9BBBDE5C06}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{f7edbe9c-2ffc-4928-ae9b-df9bbbde5c06}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3142,14 +3118,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
+        <a:blip r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3159,9 +3128,7 @@
           <a:off x="1552575" y="4962525"/>
           <a:ext cx="3343275" cy="952500"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3193,7 +3160,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -3207,12 +3174,12 @@
       <xdr:row>33</xdr:row>
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6B2F145-8850-4388-9ADE-B2C38CEC5F7B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{f6b2f145-8850-4388-9ade-b2c38cec5f7b}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3220,12 +3187,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6537960" y="4933949"/>
-          <a:ext cx="6376035" cy="981075"/>
+          <a:off x="6534150" y="4933950"/>
+          <a:ext cx="6372225" cy="981075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3234,7 +3199,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3242,16 +3207,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3262,7 +3227,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3274,7 +3239,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3286,7 +3251,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3300,7 +3265,7 @@
           <a:pPr lvl="0"/>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3313,7 +3278,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3325,7 +3290,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3336,7 +3301,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3352,7 +3317,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>19</xdr:col>
@@ -3366,12 +3331,12 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>1090</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32D1CAE3-AB1F-44E7-83A8-8CFE9F3A6676}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32d1cae3-ab1f-44e7-83a8-8cfe9f3a6676}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3379,12 +3344,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10692974" y="4231428"/>
-          <a:ext cx="6483756" cy="1262412"/>
+          <a:off x="12925425" y="4276725"/>
+          <a:ext cx="6477000" cy="1285875"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3393,7 +3356,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3401,16 +3364,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3421,7 +3384,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3433,7 +3396,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3445,7 +3408,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3459,7 +3422,7 @@
           <a:pPr lvl="0"/>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3472,7 +3435,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3490,7 +3453,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3504,12 +3467,12 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD1A3727-B21E-4010-995E-8645C474E6C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{bd1a3727-b21e-4010-995e-8645c474e6c5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3517,12 +3480,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="1971675"/>
+          <a:off x="609600" y="2143125"/>
           <a:ext cx="4391025" cy="552450"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3531,7 +3492,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3539,16 +3500,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3559,7 +3520,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3571,7 +3532,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3582,7 +3543,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3598,7 +3559,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IEA Data"/>
@@ -3733,7 +3694,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="EnergyBalance"/>
@@ -3746,28 +3707,28 @@
       <sheetData sheetId="1">
         <row r="10">
           <cell r="D10">
-            <v>-37.464700000000001</v>
+            <v>-37.4647</v>
           </cell>
           <cell r="E10">
-            <v>-317.19200000000001</v>
+            <v>-317.192</v>
           </cell>
           <cell r="F10">
             <v>0</v>
           </cell>
           <cell r="G10">
-            <v>-16.283999999999999</v>
+            <v>-16.284</v>
           </cell>
           <cell r="H10">
-            <v>-2.1499999999999998E-2</v>
+            <v>-0.0215</v>
           </cell>
           <cell r="I10">
-            <v>-528.76099999999997</v>
+            <v>-528.761</v>
           </cell>
           <cell r="J10">
-            <v>-164.50800000000001</v>
+            <v>-164.508</v>
           </cell>
           <cell r="K10">
-            <v>-0.61599999999999999</v>
+            <v>-0.616</v>
           </cell>
           <cell r="L10">
             <v>-205.88</v>
@@ -3800,27 +3761,27 @@
             <v>0</v>
           </cell>
           <cell r="V10">
-            <v>-1274.6994499999998</v>
+            <v>-1274.69945</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>-6238.7780000000012</v>
+            <v>-6238.778</v>
           </cell>
           <cell r="E11">
-            <v>-2254.2175999999999</v>
+            <v>-2254.2176</v>
           </cell>
           <cell r="F11">
             <v>0</v>
           </cell>
           <cell r="G11">
-            <v>-30.160499999999999</v>
+            <v>-30.1605</v>
           </cell>
           <cell r="H11">
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>-23.835000000000001</v>
+            <v>-23.835</v>
           </cell>
           <cell r="J11">
             <v>0</v>
@@ -3832,16 +3793,16 @@
             <v>-524.78</v>
           </cell>
           <cell r="M11">
-            <v>-33.529000000000003</v>
+            <v>-33.529</v>
           </cell>
           <cell r="N11">
             <v>-4455</v>
           </cell>
           <cell r="O11">
-            <v>-527.25918750000005</v>
+            <v>-527.2591875</v>
           </cell>
           <cell r="P11">
-            <v>-502.66000000000008</v>
+            <v>-502.66</v>
           </cell>
           <cell r="Q11">
             <v>-263.8965</v>
@@ -3850,16 +3811,16 @@
             <v>-68</v>
           </cell>
           <cell r="S11">
-            <v>-16.474499999999999</v>
+            <v>-16.4745</v>
           </cell>
           <cell r="T11">
-            <v>868.77949999999998</v>
+            <v>868.7795</v>
           </cell>
           <cell r="U11">
             <v>5790.5</v>
           </cell>
           <cell r="V11">
-            <v>-8279.3107875000023</v>
+            <v>-8279.3107875</v>
           </cell>
         </row>
         <row r="12">
@@ -3873,13 +3834,13 @@
             <v>0</v>
           </cell>
           <cell r="G12">
-            <v>-7.6189999999999998</v>
+            <v>-7.619</v>
           </cell>
           <cell r="H12">
             <v>0</v>
           </cell>
           <cell r="I12">
-            <v>-0.23350000000000001</v>
+            <v>-0.2335</v>
           </cell>
           <cell r="J12">
             <v>0</v>
@@ -3909,16 +3870,16 @@
             <v>0</v>
           </cell>
           <cell r="S12">
-            <v>-0.78449999999999998</v>
+            <v>-0.7845</v>
           </cell>
           <cell r="T12">
-            <v>329.37150000000003</v>
+            <v>329.3715</v>
           </cell>
           <cell r="U12">
             <v>0</v>
           </cell>
           <cell r="V12">
-            <v>-26.820549999999912</v>
+            <v>-26.8205499999999</v>
           </cell>
         </row>
         <row r="13">
@@ -3935,22 +3896,22 @@
             <v>5701.34</v>
           </cell>
           <cell r="H13">
-            <v>969.47799999999995</v>
+            <v>969.478</v>
           </cell>
           <cell r="I13">
-            <v>1086.3040000000001</v>
+            <v>1086.304</v>
           </cell>
           <cell r="J13">
-            <v>3354.9119999999998</v>
+            <v>3354.912</v>
           </cell>
           <cell r="K13">
-            <v>970.28800000000001</v>
+            <v>970.288</v>
           </cell>
           <cell r="L13">
-            <v>2285.1019999999999</v>
+            <v>2285.102</v>
           </cell>
           <cell r="M13">
-            <v>1299.9449999999999</v>
+            <v>1299.945</v>
           </cell>
           <cell r="N13">
             <v>0</v>
@@ -3977,12 +3938,33 @@
             <v>0</v>
           </cell>
           <cell r="V13">
-            <v>-200.86150000000021</v>
+            <v>-200.8615</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="EB1"/>
+      <sheetName val="RES_ELC"/>
+      <sheetName val="Sector_Fuels_ELC"/>
+      <sheetName val="Con_ELC"/>
+      <sheetName val="Emi"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4335,178 +4317,201 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor theme="5" tint="-0.249977111117893"/>
+    <tabColor theme="5" tint="-0.249960005283356"/>
   </sheetPr>
   <dimension ref="A1:AA17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" customWidth="1"/>
-    <col min="9" max="12" width="10.85546875" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="10.85546875" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.8571428571429" customWidth="1"/>
+    <col min="8" max="8" width="12.1428571428571" customWidth="1"/>
+    <col min="9" max="12" width="10.8571428571429" customWidth="1"/>
+    <col min="13" max="13" width="17.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="10.8571428571429" customWidth="1"/>
+    <col min="22" max="22" width="7.28571428571429" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.71428571428571" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.28571428571429" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="6" customFormat="1" ht="12.75">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
       <c r="X1" s="23" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>79</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="3:27" ht="15.75">
       <c r="C2" s="7"/>
-      <c r="D2" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="H2" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="I2" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="J2" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="K2" s="48" t="s">
-        <v>129</v>
-      </c>
-      <c r="L2" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="M2" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="N2" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" s="48" t="s">
-        <v>156</v>
-      </c>
-      <c r="P2" s="48" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q2" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="R2" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="S2" s="48" t="s">
-        <v>46</v>
-      </c>
-      <c r="T2" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" s="48" t="s">
+      <c r="D2" s="122" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="122" t="s">
+        <v>90</v>
+      </c>
+      <c r="F2" s="122" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2" s="122" t="s">
+        <v>142</v>
+      </c>
+      <c r="H2" s="122" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="122" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="122" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="122" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="122" t="s">
+        <v>59</v>
+      </c>
+      <c r="M2" s="122" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" s="122" t="s">
+        <v>57</v>
+      </c>
+      <c r="O2" s="122" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="122" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" s="122" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" s="122" t="s">
+        <v>74</v>
+      </c>
+      <c r="S2" s="122" t="s">
+        <v>53</v>
+      </c>
+      <c r="T2" s="122" t="s">
+        <v>52</v>
+      </c>
+      <c r="U2" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="V2" s="48" t="s">
-        <v>151</v>
+      <c r="V2" s="122" t="s">
+        <v>155</v>
       </c>
       <c r="X2" s="8"/>
       <c r="Y2" s="47" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="Z2" s="14" t="s">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="AA2" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="25.5" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="3" spans="3:22" ht="25.5">
       <c r="C3" s="67" t="s">
         <v>121</v>
       </c>
       <c r="D3" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="H3" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="I3" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="K3" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="L3" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="M3" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="N3" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="G3" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="H3" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="I3" s="49" t="s">
-        <v>127</v>
-      </c>
-      <c r="J3" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="K3" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="L3" s="49" t="s">
-        <v>132</v>
-      </c>
-      <c r="M3" s="49" t="s">
-        <v>133</v>
-      </c>
-      <c r="N3" s="49" t="s">
-        <v>51</v>
-      </c>
-      <c r="O3" s="49" t="s">
-        <v>159</v>
-      </c>
       <c r="P3" s="49" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="Q3" s="49" t="s">
-        <v>154</v>
+        <v>68</v>
       </c>
       <c r="R3" s="49" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="S3" s="49" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="T3" s="49" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="U3" s="49" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="V3" s="49" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B4" s="46"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="2:24" ht="12.75">
+      <c r="B4" s="123"/>
       <c r="C4" s="83" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -4529,428 +4534,428 @@
       <c r="V4" s="84"/>
       <c r="X4" s="6"/>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B5" s="50" t="s">
-        <v>56</v>
+    <row r="5" spans="2:24" ht="12.75">
+      <c r="B5" s="124" t="s">
+        <v>152</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="D5" s="51">
-        <f>[2]EB1!D10</f>
+        <f>'[2]EB1'!D10</f>
         <v>-37.464700000000001</v>
       </c>
       <c r="E5" s="51">
-        <f>[2]EB1!E10</f>
+        <f>'[2]EB1'!E10</f>
         <v>-317.19200000000001</v>
       </c>
       <c r="F5" s="51">
-        <f>[2]EB1!F10</f>
+        <f>'[2]EB1'!F10</f>
         <v>0</v>
       </c>
       <c r="G5" s="51">
-        <f>[2]EB1!G10</f>
+        <f>'[2]EB1'!G10</f>
         <v>-16.283999999999999</v>
       </c>
       <c r="H5" s="51">
-        <f>[2]EB1!H10</f>
-        <v>-2.1499999999999998E-2</v>
+        <f>'[2]EB1'!H10</f>
+        <v>-0.021499999999999998</v>
       </c>
       <c r="I5" s="51">
-        <f>[2]EB1!I10</f>
+        <f>'[2]EB1'!I10</f>
         <v>-528.76099999999997</v>
       </c>
       <c r="J5" s="51">
-        <f>[2]EB1!J10</f>
+        <f>'[2]EB1'!J10</f>
         <v>-164.50800000000001</v>
       </c>
       <c r="K5" s="51">
-        <f>[2]EB1!K10</f>
+        <f>'[2]EB1'!K10</f>
         <v>-0.61599999999999999</v>
       </c>
       <c r="L5" s="51">
-        <f>[2]EB1!L10</f>
+        <f>'[2]EB1'!L10</f>
         <v>-205.88</v>
       </c>
       <c r="M5" s="51">
-        <f>[2]EB1!M10</f>
+        <f>'[2]EB1'!M10</f>
         <v>0</v>
       </c>
       <c r="N5" s="51">
-        <f>[2]EB1!N10</f>
+        <f>'[2]EB1'!N10</f>
         <v>0</v>
       </c>
       <c r="O5" s="51">
-        <f>[2]EB1!O10</f>
+        <f>'[2]EB1'!O10</f>
         <v>-3.21225</v>
       </c>
       <c r="P5" s="51">
-        <f>[2]EB1!P10</f>
+        <f>'[2]EB1'!P10</f>
         <v>0</v>
       </c>
       <c r="Q5" s="51">
-        <f>[2]EB1!Q10</f>
+        <f>'[2]EB1'!Q10</f>
         <v>0</v>
       </c>
       <c r="R5" s="51">
-        <f>[2]EB1!R10</f>
+        <f>'[2]EB1'!R10</f>
         <v>0</v>
       </c>
       <c r="S5" s="51">
-        <f>[2]EB1!S10</f>
+        <f>'[2]EB1'!S10</f>
         <v>-0.76</v>
       </c>
       <c r="T5" s="51">
-        <f>[2]EB1!T10</f>
+        <f>'[2]EB1'!T10</f>
         <v>0</v>
       </c>
       <c r="U5" s="51">
-        <f>[2]EB1!U10</f>
+        <f>'[2]EB1'!U10</f>
         <v>0</v>
       </c>
       <c r="V5" s="85">
-        <f>[2]EB1!V10</f>
+        <f>'[2]EB1'!V10</f>
         <v>-1274.6994499999998</v>
       </c>
       <c r="X5" s="6"/>
     </row>
-    <row r="6" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="B6" s="50" t="s">
+    <row r="6" spans="2:24" ht="15">
+      <c r="B6" s="124" t="s">
         <v>48</v>
       </c>
       <c r="C6" s="60" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D6" s="54">
-        <f>[2]EB1!D11</f>
+        <f>'[2]EB1'!D11</f>
         <v>-6238.7780000000012</v>
       </c>
       <c r="E6" s="53">
-        <f>[2]EB1!E11</f>
+        <f>'[2]EB1'!E11</f>
         <v>-2254.2175999999999</v>
       </c>
       <c r="F6" s="53">
-        <f>[2]EB1!F11</f>
+        <f>'[2]EB1'!F11</f>
         <v>0</v>
       </c>
       <c r="G6" s="53">
-        <f>[2]EB1!G11</f>
+        <f>'[2]EB1'!G11</f>
         <v>-30.160499999999999</v>
       </c>
       <c r="H6" s="53">
-        <f>[2]EB1!H11</f>
+        <f>'[2]EB1'!H11</f>
         <v>0</v>
       </c>
       <c r="I6" s="53">
-        <f>[2]EB1!I11</f>
-        <v>-23.835000000000001</v>
+        <f>'[2]EB1'!I11</f>
+        <v>-23.835</v>
       </c>
       <c r="J6" s="53">
-        <f>[2]EB1!J11</f>
+        <f>'[2]EB1'!J11</f>
         <v>0</v>
       </c>
       <c r="K6" s="53">
-        <f>[2]EB1!K11</f>
+        <f>'[2]EB1'!K11</f>
         <v>0</v>
       </c>
       <c r="L6" s="53">
-        <f>[2]EB1!L11</f>
+        <f>'[2]EB1'!L11</f>
         <v>-524.78</v>
       </c>
       <c r="M6" s="53">
-        <f>[2]EB1!M11</f>
+        <f>'[2]EB1'!M11</f>
         <v>-33.529000000000003</v>
       </c>
       <c r="N6" s="53">
-        <f>[2]EB1!N11</f>
+        <f>'[2]EB1'!N11</f>
         <v>-4455</v>
       </c>
       <c r="O6" s="53">
-        <f>[2]EB1!O11</f>
+        <f>'[2]EB1'!O11</f>
         <v>-527.25918750000005</v>
       </c>
       <c r="P6" s="53">
-        <f>[2]EB1!P11</f>
+        <f>'[2]EB1'!P11</f>
         <v>-502.66000000000008</v>
       </c>
       <c r="Q6" s="53">
-        <f>[2]EB1!Q11</f>
+        <f>'[2]EB1'!Q11</f>
         <v>-263.8965</v>
       </c>
       <c r="R6" s="53">
-        <f>[2]EB1!R11</f>
+        <f>'[2]EB1'!R11</f>
         <v>-68</v>
       </c>
       <c r="S6" s="51">
-        <f>[2]EB1!S11</f>
+        <f>'[2]EB1'!S11</f>
         <v>-16.474499999999999</v>
       </c>
       <c r="T6" s="51">
-        <f>[2]EB1!T11</f>
+        <f>'[2]EB1'!T11</f>
         <v>868.77949999999998</v>
       </c>
       <c r="U6" s="53">
-        <f>[2]EB1!U11</f>
-        <v>5790.5</v>
+        <f>'[2]EB1'!U11</f>
+        <v>5790.50</v>
       </c>
       <c r="V6" s="85">
-        <f>[2]EB1!V11</f>
+        <f>'[2]EB1'!V11</f>
         <v>-8279.3107875000023</v>
       </c>
       <c r="X6" s="95"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B7" s="50" t="s">
-        <v>59</v>
+    <row r="7" spans="2:24" ht="12.75">
+      <c r="B7" s="124" t="s">
+        <v>131</v>
       </c>
       <c r="C7" s="60" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="D7" s="51">
-        <f>[2]EB1!D12</f>
+        <f>'[2]EB1'!D12</f>
         <v>-104.9074</v>
       </c>
       <c r="E7" s="51">
-        <f>[2]EB1!E12</f>
+        <f>'[2]EB1'!E12</f>
         <v>-120.5204</v>
       </c>
       <c r="F7" s="51">
-        <f>[2]EB1!F12</f>
+        <f>'[2]EB1'!F12</f>
         <v>0</v>
       </c>
       <c r="G7" s="51">
-        <f>[2]EB1!G12</f>
+        <f>'[2]EB1'!G12</f>
         <v>-7.6189999999999998</v>
       </c>
       <c r="H7" s="51">
-        <f>[2]EB1!H12</f>
+        <f>'[2]EB1'!H12</f>
         <v>0</v>
       </c>
       <c r="I7" s="51">
-        <f>[2]EB1!I12</f>
+        <f>'[2]EB1'!I12</f>
         <v>-0.23350000000000001</v>
       </c>
       <c r="J7" s="51">
-        <f>[2]EB1!J12</f>
+        <f>'[2]EB1'!J12</f>
         <v>0</v>
       </c>
       <c r="K7" s="51">
-        <f>[2]EB1!K12</f>
+        <f>'[2]EB1'!K12</f>
         <v>0</v>
       </c>
       <c r="L7" s="51">
-        <f>[2]EB1!L12</f>
-        <v>-15.2</v>
+        <f>'[2]EB1'!L12</f>
+        <v>-15.20</v>
       </c>
       <c r="M7" s="51">
-        <f>[2]EB1!M12</f>
+        <f>'[2]EB1'!M12</f>
         <v>-1.772</v>
       </c>
       <c r="N7" s="51">
-        <f>[2]EB1!N12</f>
+        <f>'[2]EB1'!N12</f>
         <v>0</v>
       </c>
       <c r="O7" s="51">
-        <f>[2]EB1!O12</f>
+        <f>'[2]EB1'!O12</f>
         <v>-105.15525</v>
       </c>
       <c r="P7" s="51">
-        <f>[2]EB1!P12</f>
+        <f>'[2]EB1'!P12</f>
         <v>0</v>
       </c>
       <c r="Q7" s="51">
-        <f>[2]EB1!Q12</f>
+        <f>'[2]EB1'!Q12</f>
         <v>0</v>
       </c>
       <c r="R7" s="51">
-        <f>[2]EB1!R12</f>
+        <f>'[2]EB1'!R12</f>
         <v>0</v>
       </c>
       <c r="S7" s="51">
-        <f>[2]EB1!S12</f>
+        <f>'[2]EB1'!S12</f>
         <v>-0.78449999999999998</v>
       </c>
       <c r="T7" s="51">
-        <f>[2]EB1!T12</f>
+        <f>'[2]EB1'!T12</f>
         <v>329.37150000000003</v>
       </c>
       <c r="U7" s="51">
-        <f>[2]EB1!U12</f>
+        <f>'[2]EB1'!U12</f>
         <v>0</v>
       </c>
       <c r="V7" s="85">
-        <f>[2]EB1!V12</f>
+        <f>'[2]EB1'!V12</f>
         <v>-26.820549999999912</v>
       </c>
       <c r="X7" s="6"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B8" s="50" t="s">
-        <v>61</v>
+    <row r="8" spans="2:22" ht="12.75">
+      <c r="B8" s="124" t="s">
+        <v>129</v>
       </c>
       <c r="C8" s="60" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="D8" s="74">
-        <f>[2]EB1!D13</f>
+        <f>'[2]EB1'!D13</f>
         <v>0</v>
       </c>
       <c r="E8" s="51">
-        <f>[2]EB1!E13</f>
+        <f>'[2]EB1'!E13</f>
         <v>0</v>
       </c>
       <c r="F8" s="51">
-        <f>[2]EB1!F13</f>
+        <f>'[2]EB1'!F13</f>
         <v>-15868.2305</v>
       </c>
       <c r="G8" s="51">
-        <f>[2]EB1!G13</f>
+        <f>'[2]EB1'!G13</f>
         <v>5701.34</v>
       </c>
       <c r="H8" s="51">
-        <f>[2]EB1!H13</f>
+        <f>'[2]EB1'!H13</f>
         <v>969.47799999999995</v>
       </c>
       <c r="I8" s="51">
-        <f>[2]EB1!I13</f>
+        <f>'[2]EB1'!I13</f>
         <v>1086.3040000000001</v>
       </c>
       <c r="J8" s="51">
-        <f>[2]EB1!J13</f>
+        <f>'[2]EB1'!J13</f>
         <v>3354.9119999999998</v>
       </c>
       <c r="K8" s="51">
-        <f>[2]EB1!K13</f>
+        <f>'[2]EB1'!K13</f>
         <v>970.28800000000001</v>
       </c>
       <c r="L8" s="51">
-        <f>[2]EB1!L13</f>
+        <f>'[2]EB1'!L13</f>
         <v>2285.1019999999999</v>
       </c>
       <c r="M8" s="51">
-        <f>[2]EB1!M13</f>
+        <f>'[2]EB1'!M13</f>
         <v>1299.9449999999999</v>
       </c>
       <c r="N8" s="51">
-        <f>[2]EB1!N13</f>
+        <f>'[2]EB1'!N13</f>
         <v>0</v>
       </c>
       <c r="O8" s="51">
-        <f>[2]EB1!O13</f>
+        <f>'[2]EB1'!O13</f>
         <v>0</v>
       </c>
       <c r="P8" s="51">
-        <f>[2]EB1!P13</f>
+        <f>'[2]EB1'!P13</f>
         <v>0</v>
       </c>
       <c r="Q8" s="51">
-        <f>[2]EB1!Q13</f>
+        <f>'[2]EB1'!Q13</f>
         <v>0</v>
       </c>
       <c r="R8" s="51">
-        <f>[2]EB1!R13</f>
+        <f>'[2]EB1'!R13</f>
         <v>0</v>
       </c>
       <c r="S8" s="51">
-        <f>[2]EB1!S13</f>
+        <f>'[2]EB1'!S13</f>
         <v>0</v>
       </c>
       <c r="T8" s="51">
-        <f>[2]EB1!T13</f>
+        <f>'[2]EB1'!T13</f>
         <v>0</v>
       </c>
       <c r="U8" s="51">
-        <f>[2]EB1!U13</f>
+        <f>'[2]EB1'!U13</f>
         <v>0</v>
       </c>
       <c r="V8" s="85">
-        <f>[2]EB1!V13</f>
+        <f>'[2]EB1'!V13</f>
         <v>-200.86150000000021</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="46"/>
+    <row r="9" spans="2:22" ht="15">
+      <c r="B9" s="123"/>
       <c r="C9" s="55" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="D9" s="58">
         <f>SUM(D5:D8)</f>
         <v>-6381.1501000000017</v>
       </c>
       <c r="E9" s="56">
-        <f t="shared" ref="E9:U9" si="0">SUM(E5:E8)</f>
+        <f>SUM(E5:E8)</f>
         <v>-2691.93</v>
       </c>
       <c r="F9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(F5:F8)</f>
         <v>-15868.2305</v>
       </c>
       <c r="G9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(G5:G8)</f>
         <v>5647.2764999999999</v>
       </c>
       <c r="H9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(H5:H8)</f>
         <v>969.45650000000001</v>
       </c>
       <c r="I9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(I5:I8)</f>
         <v>533.47450000000003</v>
       </c>
       <c r="J9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(J5:J8)</f>
         <v>3190.404</v>
       </c>
       <c r="K9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(K5:K8)</f>
         <v>969.67200000000003</v>
       </c>
       <c r="L9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(L5:L8)</f>
         <v>1539.2419999999997</v>
       </c>
       <c r="M9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(M5:M8)</f>
         <v>1264.644</v>
       </c>
       <c r="N9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(N5:N8)</f>
         <v>-4455</v>
       </c>
       <c r="O9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(O5:O8)</f>
         <v>-635.62668750000012</v>
       </c>
       <c r="P9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(P5:P8)</f>
         <v>-502.66000000000008</v>
       </c>
       <c r="Q9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(Q5:Q8)</f>
         <v>-263.8965</v>
       </c>
       <c r="R9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(R5:R8)</f>
         <v>-68</v>
       </c>
       <c r="S9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(S5:S8)</f>
         <v>-18.019000000000002</v>
       </c>
       <c r="T9" s="56">
-        <f t="shared" si="0"/>
+        <f>SUM(T5:T8)</f>
         <v>1198.1510000000001</v>
       </c>
       <c r="U9" s="56">
-        <f t="shared" si="0"/>
-        <v>5790.5</v>
+        <f>SUM(U5:U8)</f>
+        <v>5790.50</v>
       </c>
       <c r="V9" s="57">
         <f>SUM(V5:V8)</f>
         <v>-9781.6922875000037</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="12.75">
       <c r="A10" s="6"/>
       <c r="D10" s="10"/>
       <c r="F10" s="10"/>
@@ -4962,7 +4967,7 @@
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="12.75">
       <c r="A11" s="6"/>
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
@@ -4979,10 +4984,10 @@
       <c r="Q11" s="96"/>
       <c r="R11" s="96"/>
     </row>
-    <row r="12" spans="1:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="15">
       <c r="A12" s="6"/>
       <c r="C12" s="53" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="D12" s="53"/>
       <c r="E12" s="53"/>
@@ -4995,45 +5000,45 @@
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="12.75">
       <c r="A13" s="6"/>
       <c r="V13" s="8"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="12.75">
       <c r="A14" s="6"/>
       <c r="V14" s="8"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="12.75">
       <c r="A15" s="6"/>
-      <c r="C15" s="64" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="65" t="s">
-        <v>91</v>
+      <c r="C15" s="125" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="126" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="127" t="s">
+        <v>42</v>
       </c>
       <c r="V15" s="8"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="12.75">
       <c r="A16" s="6"/>
       <c r="B16" s="23" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D16" s="61" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E16" s="62" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="V16" s="8"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B17" s="50" t="s">
+    <row r="17" spans="2:5" ht="12.75">
+      <c r="B17" s="124" t="s">
         <v>48</v>
       </c>
       <c r="C17" s="90">
@@ -5044,33 +5049,33 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:M5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="4" width="6.85546875" customWidth="1"/>
-    <col min="14" max="14" width="5.42578125" customWidth="1"/>
+    <col min="1" max="1" width="1.85714285714286" customWidth="1"/>
+    <col min="2" max="2" width="7.71428571428571" customWidth="1"/>
+    <col min="3" max="4" width="6.85714285714286" customWidth="1"/>
+    <col min="14" max="14" width="5.42857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="5:6" ht="12.75">
       <c r="E1" s="11"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="2:13" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" ht="18">
       <c r="B2" s="78" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="4" spans="2:13" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="5:13" ht="18">
       <c r="E4" s="119" t="s">
         <v>149</v>
       </c>
@@ -5083,9 +5088,9 @@
       <c r="L4" s="120"/>
       <c r="M4" s="121"/>
     </row>
-    <row r="5" spans="2:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="5:13" ht="12.75" customHeight="1">
       <c r="E5" s="79" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F5" s="79"/>
       <c r="G5" s="79"/>
@@ -5101,48 +5106,48 @@
     <mergeCell ref="E4:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:R33"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:R33"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28571428571429" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="61.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" customWidth="1"/>
+    <col min="9" max="9" width="2.14285714285714" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.4285714285714" customWidth="1"/>
+    <col min="11" max="11" width="7.14285714285714" customWidth="1"/>
+    <col min="12" max="12" width="14.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="61.7142857142857" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.14285714285714" customWidth="1"/>
+    <col min="15" max="15" width="10.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15">
       <c r="B1" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>67</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>79</v>
@@ -5152,7 +5157,7 @@
       </c>
       <c r="H1" s="39"/>
     </row>
-    <row r="2" spans="2:18" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="31.5">
       <c r="B2" s="14" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
@@ -5162,7 +5167,7 @@
         <v>Electricity Plants</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="E2" s="14" t="str">
         <f>'EB1'!Z2</f>
@@ -5188,7 +5193,7 @@
       <c r="Q2" s="107"/>
       <c r="R2" s="107"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="10:18" ht="12.75">
       <c r="J3" s="108" t="s">
         <v>7</v>
       </c>
@@ -5217,12 +5222,16 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" s="6" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="6" customFormat="1" ht="24" thickBot="1">
+      <c r="A4" s="6"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
+      <c r="F4" s="6"/>
       <c r="G4" s="13"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
       <c r="J4" s="110" t="s">
         <v>35</v>
       </c>
@@ -5251,7 +5260,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:18" ht="12.75">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -5272,7 +5281,7 @@
         <v>Electricity Plants Solid Fuels</v>
       </c>
       <c r="N5" s="111" t="str">
-        <f t="shared" ref="N5:N12" si="0">$E$2</f>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O5" s="111"/>
@@ -5280,7 +5289,7 @@
       <c r="Q5" s="111"/>
       <c r="R5" s="111"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:18" ht="12.75">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -5299,7 +5308,7 @@
         <v>Electricity Plants Natural Gas</v>
       </c>
       <c r="N6" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O6" s="111"/>
@@ -5307,7 +5316,7 @@
       <c r="Q6" s="111"/>
       <c r="R6" s="111"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:18" ht="12.75">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -5326,7 +5335,7 @@
         <v>Electricity Plants oil</v>
       </c>
       <c r="N7" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O7" s="111"/>
@@ -5334,7 +5343,7 @@
       <c r="Q7" s="111"/>
       <c r="R7" s="111"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:18" ht="12.75">
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -5353,7 +5362,7 @@
         <v>Electricity Plants Nuclear Energy</v>
       </c>
       <c r="N8" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O8" s="111"/>
@@ -5361,7 +5370,7 @@
       <c r="Q8" s="111"/>
       <c r="R8" s="111"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:18" ht="12.75">
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -5380,7 +5389,7 @@
         <v>Electricity Plants Biomass</v>
       </c>
       <c r="N9" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O9" s="111"/>
@@ -5388,7 +5397,7 @@
       <c r="Q9" s="111"/>
       <c r="R9" s="111"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:18" ht="12.75">
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -5407,7 +5416,7 @@
         <v>Electricity Plants Hydro power</v>
       </c>
       <c r="N10" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O10" s="111"/>
@@ -5415,7 +5424,7 @@
       <c r="Q10" s="111"/>
       <c r="R10" s="111"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:18" ht="12.75">
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -5434,7 +5443,7 @@
         <v>Electricity Plants Wind energy</v>
       </c>
       <c r="N11" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O11" s="111"/>
@@ -5442,7 +5451,7 @@
       <c r="Q11" s="111"/>
       <c r="R11" s="111"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:18" ht="12.75">
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -5461,7 +5470,7 @@
         <v>Electricity Plants Solar energy</v>
       </c>
       <c r="N12" s="111" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O12" s="111"/>
@@ -5469,11 +5478,11 @@
       <c r="Q12" s="111"/>
       <c r="R12" s="111"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="12:13" ht="12.75">
       <c r="L13" s="27"/>
       <c r="M13" s="29"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="4:18" ht="12.75">
       <c r="D14" s="4" t="s">
         <v>13</v>
       </c>
@@ -5491,7 +5500,7 @@
       <c r="Q14" s="113"/>
       <c r="R14" s="113"/>
     </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:18" ht="12.75">
       <c r="B15" s="20" t="s">
         <v>1</v>
       </c>
@@ -5502,7 +5511,7 @@
         <v>6</v>
       </c>
       <c r="E15" s="82" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="F15" s="80" t="s">
         <v>123</v>
@@ -5541,7 +5550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" ht="23.25" thickBot="1">
       <c r="B16" s="19" t="s">
         <v>37</v>
       </c>
@@ -5552,7 +5561,7 @@
         <v>33</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="F16" s="19" t="s">
         <v>34</v>
@@ -5591,19 +5600,19 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" ht="13.5" thickBot="1">
       <c r="B17" s="18" t="s">
         <v>76</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17" t="str">
+      <c r="E17" s="105"/>
+      <c r="F17" s="105" t="str">
         <f>F2&amp;"a"</f>
         <v>M€2005a</v>
       </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17" t="s">
+      <c r="G17" s="105"/>
+      <c r="H17" s="105" t="s">
         <v>77</v>
       </c>
       <c r="J17" s="110" t="s">
@@ -5618,7 +5627,7 @@
       <c r="Q17" s="114"/>
       <c r="R17" s="114"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" ht="12.75">
       <c r="B18" s="25" t="str">
         <f>Sector_Fuels_ELC!L18</f>
         <v>FTE-ELCCOA</v>
@@ -5640,30 +5649,30 @@
         <v>30</v>
       </c>
       <c r="J18" s="115" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="K18" s="116"/>
       <c r="L18" s="111" t="str">
-        <f t="shared" ref="L18:L25" si="1">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-ELCCOA</v>
       </c>
       <c r="M18" s="112" t="str">
-        <f t="shared" ref="M18:M25" si="2">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Electricity Plants Solid Fuels</v>
       </c>
       <c r="N18" s="111" t="str">
-        <f t="shared" ref="N18:N25" si="3">$E$2</f>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O18" s="111" t="str">
-        <f t="shared" ref="O18:O25" si="4">$E$2&amp;"a"</f>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P18" s="111"/>
       <c r="Q18" s="111"/>
       <c r="R18" s="111"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" ht="12.75">
       <c r="B19" s="25" t="str">
         <f>Sector_Fuels_ELC!L19</f>
         <v>FTE-ELCGAS</v>
@@ -5687,26 +5696,26 @@
       <c r="J19" s="113"/>
       <c r="K19" s="116"/>
       <c r="L19" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L6</f>
         <v>FTE-ELCGAS</v>
       </c>
       <c r="M19" s="112" t="str">
-        <f t="shared" si="2"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M6</f>
         <v>Sector Fuel Technology Existing Electricity Plants Natural Gas</v>
       </c>
       <c r="N19" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O19" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P19" s="111"/>
       <c r="Q19" s="111"/>
       <c r="R19" s="111"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" ht="12.75">
       <c r="B20" s="25" t="str">
         <f>Sector_Fuels_ELC!L20</f>
         <v>FTE-ELCOIL</v>
@@ -5721,7 +5730,7 @@
       </c>
       <c r="E20" s="70">
         <f>-'EB1'!G$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>4.9257354796510562E-2</v>
+        <v>0.049257354796510562</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="71">
@@ -5733,26 +5742,26 @@
       <c r="J20" s="116"/>
       <c r="K20" s="116"/>
       <c r="L20" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L7</f>
         <v>FTE-ELCOIL</v>
       </c>
       <c r="M20" s="112" t="str">
-        <f t="shared" si="2"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M7</f>
         <v>Sector Fuel Technology Existing Electricity Plants oil</v>
       </c>
       <c r="N20" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O20" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P20" s="111"/>
       <c r="Q20" s="111"/>
       <c r="R20" s="111"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:18" ht="12.75">
       <c r="B21" s="25"/>
       <c r="C21" t="str">
         <f>'EB1'!I$2</f>
@@ -5761,7 +5770,7 @@
       <c r="D21" s="25"/>
       <c r="E21" s="70">
         <f>-'EB1'!I$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>3.8926710484734312E-2</v>
+        <v>0.038926710484734312</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="71"/>
@@ -5769,26 +5778,26 @@
       <c r="J21" s="117"/>
       <c r="K21" s="117"/>
       <c r="L21" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L8</f>
         <v>FTE-ELCNUC</v>
       </c>
       <c r="M21" s="112" t="str">
-        <f t="shared" si="2"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M8</f>
         <v>Sector Fuel Technology Existing Electricity Plants Nuclear Energy</v>
       </c>
       <c r="N21" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O21" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P21" s="117"/>
       <c r="Q21" s="117"/>
       <c r="R21" s="111"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:18" ht="12.75">
       <c r="B22" s="25"/>
       <c r="C22" t="str">
         <f>'EB1'!L$2</f>
@@ -5805,26 +5814,26 @@
       <c r="J22" s="111"/>
       <c r="K22" s="111"/>
       <c r="L22" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L9</f>
         <v>FTE-ELCBIO</v>
       </c>
       <c r="M22" s="112" t="str">
-        <f t="shared" si="2"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M9</f>
         <v>Sector Fuel Technology Existing Electricity Plants Biomass</v>
       </c>
       <c r="N22" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O22" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P22" s="111"/>
       <c r="Q22" s="111"/>
       <c r="R22" s="111"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:18" ht="12.75">
       <c r="B23" s="25"/>
       <c r="C23" t="str">
         <f>'EB1'!M$2</f>
@@ -5833,7 +5842,7 @@
       <c r="D23" s="25"/>
       <c r="E23" s="70">
         <f>-'EB1'!M$6/-SUM('EB1'!$G$6:$M$6)</f>
-        <v>5.4758702573637796E-2</v>
+        <v>0.054758702573637796</v>
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="71"/>
@@ -5841,26 +5850,26 @@
       <c r="J23" s="113"/>
       <c r="K23" s="113"/>
       <c r="L23" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L10</f>
         <v>FTE-ELCHYD</v>
       </c>
       <c r="M23" s="112" t="str">
-        <f t="shared" si="2"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M10</f>
         <v>Sector Fuel Technology Existing Electricity Plants Hydro power</v>
       </c>
       <c r="N23" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O23" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P23" s="111"/>
       <c r="Q23" s="113"/>
       <c r="R23" s="113"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:18" ht="12.75">
       <c r="B24" s="28" t="str">
         <f>Sector_Fuels_ELC!L21</f>
         <v>FTE-ELCNUC</v>
@@ -5884,26 +5893,26 @@
       <c r="J24" s="113"/>
       <c r="K24" s="113"/>
       <c r="L24" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L11</f>
         <v>FTE-ELCWIN</v>
       </c>
       <c r="M24" s="112" t="str">
-        <f t="shared" si="2"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M11</f>
         <v>Sector Fuel Technology Existing Electricity Plants Wind energy</v>
       </c>
       <c r="N24" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O24" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P24" s="111"/>
       <c r="Q24" s="113"/>
       <c r="R24" s="113"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:18" ht="12.75">
       <c r="B25" s="28" t="str">
         <f>Sector_Fuels_ELC!L22</f>
         <v>FTE-ELCBIO</v>
@@ -5927,26 +5936,26 @@
       <c r="J25" s="113"/>
       <c r="K25" s="113"/>
       <c r="L25" s="111" t="str">
-        <f t="shared" si="1"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L12</f>
         <v>FTE-ELCSOL</v>
       </c>
       <c r="M25" s="112" t="str">
-        <f t="shared" si="2"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M12</f>
         <v>Sector Fuel Technology Existing Electricity Plants Solar energy</v>
       </c>
       <c r="N25" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O25" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P25" s="113"/>
       <c r="Q25" s="113"/>
       <c r="R25" s="113"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:8" ht="12.75">
       <c r="B26" s="28" t="str">
         <f>Sector_Fuels_ELC!L23</f>
         <v>FTE-ELCHYD</v>
@@ -5968,7 +5977,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:8" ht="12.75">
       <c r="B27" s="28" t="str">
         <f>Sector_Fuels_ELC!L24</f>
         <v>FTE-ELCWIN</v>
@@ -5990,7 +5999,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:8" ht="12.75">
       <c r="B28" s="28" t="str">
         <f>Sector_Fuels_ELC!L25</f>
         <v>FTE-ELCSOL</v>
@@ -6012,13 +6021,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:3" ht="12.75">
       <c r="B32" s="52"/>
       <c r="C32" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:3" ht="12.75">
       <c r="B33" s="68"/>
       <c r="C33" s="1" t="s">
         <v>145</v>
@@ -6026,46 +6035,47 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId4"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:AB65536"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:AB65536"/>
+  <sheetFormatPr defaultColWidth="8.85428571428571" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" style="25" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" style="25" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.4285714285714" style="25" customWidth="1"/>
+    <col min="3" max="3" width="12.1428571428571" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.2857142857143" style="25" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12" style="25" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="13" style="25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85714285714286" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.14285714285714" style="25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85714285714286" style="25" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.85714285714286" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="25" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.2857142857143" style="25" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="2" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.28515625" customWidth="1"/>
-    <col min="25" max="25" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5714285714286" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.14285714285714" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.42857142857143" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="43.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.28571428571429" customWidth="1"/>
+    <col min="25" max="25" width="11.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5714285714286" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.85546875" style="25"/>
+    <col min="28" max="28" width="8.14285714285714" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.85714285714286" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:28" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="30">
+      <c r="A1" s="25"/>
       <c r="B1" s="24" t="s">
         <v>65</v>
       </c>
@@ -6073,22 +6083,34 @@
         <v>67</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="E1" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F1" s="24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="H1" s="24" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="2:28" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="27"/>
+    </row>
+    <row r="2" spans="1:28" ht="31.5">
+      <c r="A2" s="25"/>
       <c r="B2" s="14" t="str">
         <f>'EB1'!B6</f>
         <v>ELC</v>
@@ -6098,14 +6120,14 @@
         <v>Electricity Plants</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="E2" s="14" t="str">
         <f>'EB1'!Z2</f>
         <v>PJ</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G2" s="14" t="str">
         <f>'EB1'!Y2</f>
@@ -6114,6 +6136,17 @@
       <c r="H2" s="14" t="s">
         <v>84</v>
       </c>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="27"/>
       <c r="T2" s="106" t="s">
         <v>14</v>
       </c>
@@ -6126,7 +6159,26 @@
       <c r="AA2" s="107"/>
       <c r="AB2" s="107"/>
     </row>
-    <row r="3" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:28" ht="12.75">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="27"/>
       <c r="T3" s="108" t="s">
         <v>7</v>
       </c>
@@ -6155,24 +6207,35 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:28" s="26" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" s="26" customFormat="1" ht="30.75" thickBot="1">
+      <c r="A4" s="26"/>
       <c r="B4" s="33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>122</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="G4" s="26"/>
       <c r="H4" s="13"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
       <c r="K4" s="13"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
       <c r="S4" s="27"/>
       <c r="T4" s="110" t="s">
         <v>35</v>
@@ -6202,24 +6265,35 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:28" s="26" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" s="26" customFormat="1" ht="15.75">
+      <c r="A5" s="26"/>
       <c r="B5" s="32" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>85</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="G5" s="26"/>
       <c r="H5" s="13"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
       <c r="K5" s="13"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="26"/>
+      <c r="Q5" s="26"/>
+      <c r="R5" s="26"/>
       <c r="S5" s="27"/>
       <c r="T5" s="115" t="s">
         <v>64</v>
@@ -6239,16 +6313,35 @@
       </c>
       <c r="Y5" s="115"/>
       <c r="Z5" s="115" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="AA5" s="115"/>
       <c r="AB5" s="115" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" ht="12.75">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="25"/>
+      <c r="S6" s="27"/>
       <c r="T6" s="113" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="U6" s="113"/>
       <c r="V6" s="113" t="str">
@@ -6268,11 +6361,33 @@
       <c r="AA6" s="113"/>
       <c r="AB6" s="113"/>
     </row>
-    <row r="7" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" ht="12.75">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="27"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" ht="12.75">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
@@ -6281,10 +6396,16 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="3"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
       <c r="Q8" s="26"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="27"/>
       <c r="T8" s="106" t="s">
         <v>15</v>
       </c>
@@ -6297,7 +6418,8 @@
       <c r="AA8" s="107"/>
       <c r="AB8" s="107"/>
     </row>
-    <row r="9" spans="2:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" ht="12.75" customHeight="1">
+      <c r="A9" s="25"/>
       <c r="B9" s="21" t="s">
         <v>1</v>
       </c>
@@ -6308,44 +6430,44 @@
         <v>6</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="G9" s="80" t="s">
         <v>123</v>
       </c>
       <c r="H9" s="80" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="I9" s="80" t="s">
         <v>73</v>
       </c>
       <c r="J9" s="80" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K9" s="80" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="L9" s="80" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="M9" s="80" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="N9" s="80" t="s">
         <v>70</v>
       </c>
       <c r="O9" s="80" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="P9" s="80" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="Q9" s="30"/>
       <c r="R9" s="101" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="S9" s="35"/>
       <c r="T9" s="108" t="s">
@@ -6376,7 +6498,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:28" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="23.25" thickBot="1">
+      <c r="A10" s="25"/>
       <c r="B10" s="19" t="s">
         <v>37</v>
       </c>
@@ -6387,44 +6510,44 @@
         <v>33</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="G10" s="19" t="s">
         <v>34</v>
       </c>
       <c r="H10" s="86" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I10" s="19" t="s">
         <v>75</v>
       </c>
       <c r="J10" s="86" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L10" s="19" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="M10" s="19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N10" s="19" t="s">
         <v>160</v>
       </c>
       <c r="O10" s="19" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="P10" s="19" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="Q10" s="26"/>
       <c r="R10" s="38" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="S10" s="36"/>
       <c r="T10" s="110" t="s">
@@ -6455,7 +6578,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:28" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="13.5" thickBot="1">
+      <c r="A11" s="25"/>
       <c r="B11" s="18" t="s">
         <v>76</v>
       </c>
@@ -6469,7 +6593,7 @@
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="G11" s="17" t="str">
+      <c r="G11" s="105" t="str">
         <f>$F$2</f>
         <v>GW</v>
       </c>
@@ -6477,28 +6601,28 @@
         <f>$F$2</f>
         <v>GW</v>
       </c>
-      <c r="I11" s="17"/>
+      <c r="I11" s="105"/>
       <c r="J11" s="81"/>
-      <c r="K11" s="17" t="str">
+      <c r="K11" s="105" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2005/GW</v>
       </c>
-      <c r="L11" s="17" t="str">
+      <c r="L11" s="105" t="str">
         <f>$G$2&amp;"/"&amp;$F$2</f>
         <v>M€2005/GW</v>
       </c>
-      <c r="M11" s="17" t="str">
+      <c r="M11" s="105" t="str">
         <f>$G$2&amp;"/"&amp;$E$2</f>
         <v>M€2005/PJ</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="N11" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="O11" s="17" t="str">
+      <c r="O11" s="105" t="str">
         <f>$E$2&amp;"/"&amp;$F$2</f>
         <v>PJ/GW</v>
       </c>
-      <c r="P11" s="17"/>
+      <c r="P11" s="105"/>
       <c r="Q11" s="26"/>
       <c r="R11" s="102" t="s">
         <v>121</v>
@@ -6516,9 +6640,10 @@
       <c r="AA11" s="110"/>
       <c r="AB11" s="110"/>
     </row>
-    <row r="12" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:28" ht="12.75">
+      <c r="A12" s="25"/>
       <c r="B12" s="25" t="str">
-        <f t="shared" ref="B12:B19" si="0">V12</f>
+        <f>V12</f>
         <v>ELCTECOA00</v>
       </c>
       <c r="C12" s="25" t="str">
@@ -6526,9 +6651,11 @@
         <v>ELCCOA</v>
       </c>
       <c r="D12" s="25" t="str">
-        <f t="shared" ref="D12:D19" si="1">$V$5</f>
+        <f>$V$5</f>
         <v>ELC</v>
       </c>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
       <c r="G12" s="98">
         <f>(-'EB1'!$D$6*$I$12)/($J$12*$O$12)</f>
         <v>89.372771062763022</v>
@@ -6545,7 +6672,7 @@
         <v>40</v>
       </c>
       <c r="M12" s="76">
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="N12" s="75">
         <v>30</v>
@@ -6558,12 +6685,12 @@
       </c>
       <c r="Q12" s="26"/>
       <c r="R12" s="34">
-        <f t="shared" ref="R12:R19" si="2">G12*$J12*$O12</f>
+        <f>G12*$J12*$O12</f>
         <v>2395.6907520000004</v>
       </c>
       <c r="S12" s="100"/>
       <c r="T12" s="111" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="U12" s="111"/>
       <c r="V12" s="111" t="str">
@@ -6575,22 +6702,23 @@
         <v>Power Plants Existing00 - Solid Fuels</v>
       </c>
       <c r="X12" s="111" t="str">
-        <f t="shared" ref="X12:X19" si="3">$E$2</f>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="Y12" s="111" t="str">
-        <f t="shared" ref="Y12:Y19" si="4">$F$2</f>
+        <f>$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z12" s="115" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="AA12" s="111"/>
       <c r="AB12" s="111"/>
     </row>
-    <row r="13" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" ht="12.75">
+      <c r="A13" s="25"/>
       <c r="B13" s="25" t="str">
-        <f t="shared" si="0"/>
+        <f>V13</f>
         <v>ELCTEGAS00</v>
       </c>
       <c r="C13" s="25" t="str">
@@ -6598,9 +6726,11 @@
         <v>ELCGAS</v>
       </c>
       <c r="D13" s="25" t="str">
-        <f t="shared" si="1"/>
+        <f>$V$5</f>
         <v>ELC</v>
       </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
       <c r="G13" s="98">
         <f>(-'EB1'!$E$6*$I$13)/($J$13*$O$13)</f>
         <v>41.450437783149788</v>
@@ -6617,7 +6747,7 @@
         <v>35</v>
       </c>
       <c r="M13" s="76">
-        <v>0.4</v>
+        <v>0.40</v>
       </c>
       <c r="N13" s="75">
         <v>20</v>
@@ -6630,7 +6760,7 @@
       </c>
       <c r="Q13" s="26"/>
       <c r="R13" s="34">
-        <f t="shared" si="2"/>
+        <f>G13*$J13*$O13</f>
         <v>1111.1038550399999</v>
       </c>
       <c r="S13" s="37"/>
@@ -6645,20 +6775,21 @@
         <v>Power Plants Existing00 - Natural Gas</v>
       </c>
       <c r="X13" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="Y13" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z13" s="111"/>
       <c r="AA13" s="111"/>
       <c r="AB13" s="111"/>
     </row>
-    <row r="14" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:28" ht="12.75">
+      <c r="A14" s="25"/>
       <c r="B14" s="25" t="str">
-        <f t="shared" si="0"/>
+        <f>V14</f>
         <v>ELCTEOIL00</v>
       </c>
       <c r="C14" s="25" t="str">
@@ -6666,9 +6797,11 @@
         <v>ELCOIL</v>
       </c>
       <c r="D14" s="25" t="str">
-        <f t="shared" si="1"/>
+        <f>$V$5</f>
         <v>ELC</v>
       </c>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="98">
         <f>((-SUM('EB1'!G6:M6)*$I$14)/($J$14*$O$14))</f>
         <v>5.710602448742053</v>
@@ -6685,7 +6818,7 @@
         <v>20</v>
       </c>
       <c r="M14" s="94">
-        <v>0.2</v>
+        <v>0.20</v>
       </c>
       <c r="N14" s="93">
         <v>30</v>
@@ -6698,7 +6831,7 @@
       </c>
       <c r="Q14" s="26"/>
       <c r="R14" s="34">
-        <f t="shared" si="2"/>
+        <f>G14*$J14*$O14</f>
         <v>153.07612499999996</v>
       </c>
       <c r="S14" s="37"/>
@@ -6713,20 +6846,21 @@
         <v>Power Plants Existing00 - Crude oil</v>
       </c>
       <c r="X14" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="Y14" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z14" s="111"/>
       <c r="AA14" s="111"/>
       <c r="AB14" s="111"/>
     </row>
-    <row r="15" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" ht="12.75">
+      <c r="A15" s="25"/>
       <c r="B15" s="28" t="str">
-        <f t="shared" si="0"/>
+        <f>V15</f>
         <v>ELCNENUC00</v>
       </c>
       <c r="C15" s="25" t="str">
@@ -6734,7 +6868,7 @@
         <v>ELCNUC</v>
       </c>
       <c r="D15" s="28" t="str">
-        <f t="shared" si="1"/>
+        <f>$V$5</f>
         <v>ELC</v>
       </c>
       <c r="E15" s="28"/>
@@ -6751,7 +6885,7 @@
         <v>0.33</v>
       </c>
       <c r="J15" s="94">
-        <v>0.9</v>
+        <v>0.90</v>
       </c>
       <c r="K15" s="93"/>
       <c r="L15" s="94">
@@ -6769,7 +6903,7 @@
       </c>
       <c r="Q15" s="28"/>
       <c r="R15" s="34">
-        <f t="shared" si="2"/>
+        <f>G15*$J15*$O15</f>
         <v>1470.1500000000003</v>
       </c>
       <c r="S15" s="37"/>
@@ -6784,22 +6918,23 @@
         <v>Power Plants Existing00 - Nuclear Energy</v>
       </c>
       <c r="X15" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="Y15" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z15" s="115" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="AA15" s="111"/>
       <c r="AB15" s="111"/>
     </row>
-    <row r="16" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" ht="12.75">
+      <c r="A16" s="25"/>
       <c r="B16" s="28" t="str">
-        <f t="shared" si="0"/>
+        <f>V16</f>
         <v>ELCREBIO00</v>
       </c>
       <c r="C16" s="25" t="str">
@@ -6807,7 +6942,7 @@
         <v>ELCBIO</v>
       </c>
       <c r="D16" s="28" t="str">
-        <f t="shared" si="1"/>
+        <f>$V$5</f>
         <v>ELC</v>
       </c>
       <c r="E16" s="28"/>
@@ -6821,7 +6956,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="J16" s="73">
-        <v>0.6</v>
+        <v>0.60</v>
       </c>
       <c r="K16" s="73"/>
       <c r="L16" s="74">
@@ -6841,7 +6976,7 @@
       </c>
       <c r="Q16" s="28"/>
       <c r="R16" s="34">
-        <f t="shared" si="2"/>
+        <f>G16*$J16*$O16</f>
         <v>147.63257250000001</v>
       </c>
       <c r="S16" s="37"/>
@@ -6856,20 +6991,21 @@
         <v>Power Plants Existing00 - Biomass</v>
       </c>
       <c r="X16" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="Y16" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z16" s="115"/>
       <c r="AA16" s="111"/>
       <c r="AB16" s="111"/>
     </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:28" ht="12.75">
+      <c r="A17" s="25"/>
       <c r="B17" s="28" t="str">
-        <f t="shared" si="0"/>
+        <f>V17</f>
         <v>ELCREHYD00</v>
       </c>
       <c r="C17" s="25" t="str">
@@ -6877,7 +7013,7 @@
         <v>ELCHYD</v>
       </c>
       <c r="D17" s="28" t="str">
-        <f t="shared" si="1"/>
+        <f>$V$5</f>
         <v>ELC</v>
       </c>
       <c r="E17" s="74">
@@ -6892,7 +7028,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="73">
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="K17" s="73"/>
       <c r="L17" s="74">
@@ -6908,7 +7044,7 @@
         <v>31.536000000000001</v>
       </c>
       <c r="P17" s="94">
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="Q17" s="28"/>
       <c r="R17" s="34">
@@ -6927,20 +7063,21 @@
         <v>Power Plants Existing00 - Hydro power</v>
       </c>
       <c r="X17" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="Y17" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z17" s="111"/>
       <c r="AA17" s="111"/>
       <c r="AB17" s="111"/>
     </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:28" ht="12.75">
+      <c r="A18" s="25"/>
       <c r="B18" s="28" t="str">
-        <f t="shared" si="0"/>
+        <f>V18</f>
         <v>ELCREWIN00</v>
       </c>
       <c r="C18" s="25" t="str">
@@ -6948,7 +7085,7 @@
         <v>ELCWIN</v>
       </c>
       <c r="D18" s="28" t="str">
-        <f t="shared" si="1"/>
+        <f>$V$5</f>
         <v>ELC</v>
       </c>
       <c r="E18" s="28"/>
@@ -6969,7 +7106,7 @@
         <v>35</v>
       </c>
       <c r="M18" s="73">
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="N18" s="74">
         <v>20</v>
@@ -6978,11 +7115,11 @@
         <v>31.536000000000001</v>
       </c>
       <c r="P18" s="94">
-        <v>0.3</v>
+        <v>0.30</v>
       </c>
       <c r="Q18" s="28"/>
       <c r="R18" s="34">
-        <f t="shared" si="2"/>
+        <f>G18*$J18*$O18</f>
         <v>263.8965</v>
       </c>
       <c r="S18" s="37"/>
@@ -6997,20 +7134,21 @@
         <v>Power Plants Existing00 - Wind energy</v>
       </c>
       <c r="X18" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="Y18" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z18" s="111"/>
       <c r="AA18" s="111"/>
       <c r="AB18" s="111"/>
     </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:28" ht="12.75">
+      <c r="A19" s="25"/>
       <c r="B19" s="28" t="str">
-        <f t="shared" si="0"/>
+        <f>V19</f>
         <v>ELCRESOL00</v>
       </c>
       <c r="C19" s="25" t="str">
@@ -7018,7 +7156,7 @@
         <v>ELCSOL</v>
       </c>
       <c r="D19" s="28" t="str">
-        <f t="shared" si="1"/>
+        <f>$V$5</f>
         <v>ELC</v>
       </c>
       <c r="E19" s="28"/>
@@ -7032,7 +7170,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="73">
-        <v>0.3</v>
+        <v>0.30</v>
       </c>
       <c r="K19" s="73"/>
       <c r="L19" s="74">
@@ -7046,11 +7184,11 @@
         <v>31.536000000000001</v>
       </c>
       <c r="P19" s="94">
-        <v>0.2</v>
+        <v>0.20</v>
       </c>
       <c r="Q19" s="28"/>
       <c r="R19" s="34">
-        <f t="shared" si="2"/>
+        <f>G19*$J19*$O19</f>
         <v>68</v>
       </c>
       <c r="S19" s="37"/>
@@ -7065,62 +7203,151 @@
         <v>Power Plants Existing00 - Solar energy</v>
       </c>
       <c r="X19" s="111" t="str">
-        <f t="shared" si="3"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="Y19" s="111" t="str">
-        <f t="shared" si="4"/>
+        <f>$F$2</f>
         <v>GW</v>
       </c>
       <c r="Z19" s="111"/>
       <c r="AA19" s="111"/>
       <c r="AB19" s="111"/>
     </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" ht="12.75">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="27"/>
+    </row>
+    <row r="21" spans="1:19" ht="12.75">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
       <c r="R21" s="97"/>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="S21" s="27"/>
+    </row>
+    <row r="22" spans="1:19" ht="12.75">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
       <c r="R22" s="97"/>
-    </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="S22" s="27"/>
+    </row>
+    <row r="23" spans="1:19" ht="12.75">
+      <c r="A23" s="25"/>
       <c r="B23" s="52"/>
       <c r="C23" s="1" t="s">
         <v>144</v>
       </c>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
       <c r="R23" s="97"/>
-    </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="S23" s="27"/>
+    </row>
+    <row r="24" spans="1:19" ht="12.75">
+      <c r="A24" s="25"/>
       <c r="B24" s="68"/>
       <c r="C24" s="1" t="s">
         <v>145</v>
       </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
       <c r="R24" s="97"/>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="S24" s="27"/>
+    </row>
+    <row r="25" spans="18:18" ht="12.75">
       <c r="R25" s="97"/>
     </row>
-    <row r="65536" spans="19:19" x14ac:dyDescent="0.2">
+    <row r="65536" spans="19:19" ht="12.75">
       <c r="S65536" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId4"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:J24"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A3:J24"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:10" ht="17.45" customHeight="1">
       <c r="B3" s="42" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C3" s="42"/>
       <c r="D3" s="42"/>
@@ -7131,7 +7358,8 @@
       <c r="I3" s="42"/>
       <c r="J3" s="42"/>
     </row>
-    <row r="4" spans="2:10" s="6" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="6" customFormat="1" ht="17.45" customHeight="1">
+      <c r="A4" s="6"/>
       <c r="B4" s="43"/>
       <c r="C4" s="43"/>
       <c r="D4" s="43"/>
@@ -7139,7 +7367,7 @@
       <c r="F4" s="43"/>
       <c r="G4" s="43"/>
     </row>
-    <row r="5" spans="2:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="18">
       <c r="B5" s="40" t="s">
         <v>138</v>
       </c>
@@ -7147,7 +7375,7 @@
       <c r="F5" s="31"/>
       <c r="G5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="13.5" thickBot="1">
       <c r="B6" s="45" t="s">
         <v>0</v>
       </c>
@@ -7167,24 +7395,24 @@
       <c r="G6" s="44"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" ht="13.5" thickBot="1">
       <c r="B7" s="18" t="s">
         <v>76</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F7" s="88"/>
       <c r="G7" s="88"/>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:8" ht="12.75">
       <c r="B8" s="25" t="str">
         <f>Con_ELC!$V$6</f>
         <v>ELCCO2</v>
@@ -7193,7 +7421,7 @@
         <v>95</v>
       </c>
       <c r="D8" s="73">
-        <v>56.1</v>
+        <v>56.10</v>
       </c>
       <c r="E8" s="73">
         <v>76.400000000000006</v>
@@ -7202,21 +7430,21 @@
       <c r="G8" s="89"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="6:7" ht="12.75">
       <c r="F9" s="31"/>
       <c r="G9" s="31"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="6:7" ht="12.75">
       <c r="F10" s="31"/>
       <c r="G10" s="31"/>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3" ht="12.75">
       <c r="B23" s="52"/>
       <c r="C23" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" ht="12.75">
       <c r="B24" s="68"/>
       <c r="C24" s="1" t="s">
         <v>145</v>
